--- a/public/WEEK5_SHOPPING_LIST.xlsx
+++ b/public/WEEK5_SHOPPING_LIST.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Vecka 5 Inköpslista" sheetId="1" r:id="rId1"/>
+    <sheet name="Vecka 5" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -490,13 +490,10 @@
         <v>Frukt/Grönt</v>
       </c>
       <c r="C6" t="str">
-        <v>ime</v>
+        <v>lime</v>
       </c>
       <c r="D6">
         <v>0.75</v>
-      </c>
-      <c r="E6" t="str">
-        <v>l</v>
       </c>
     </row>
     <row r="7">
@@ -566,13 +563,10 @@
         <v>Frukt/Grönt</v>
       </c>
       <c r="C11" t="str">
-        <v>ul lök</v>
+        <v>gul lök</v>
       </c>
       <c r="D11">
         <v>1</v>
-      </c>
-      <c r="E11" t="str">
-        <v>g</v>
       </c>
     </row>
     <row r="12">
@@ -1124,13 +1118,10 @@
         <v>Kryddor/smaksättare</v>
       </c>
       <c r="C47" t="str">
-        <v>färsk basilika</v>
+        <v>msk färsk basilika</v>
       </c>
       <c r="D47">
         <v>2</v>
-      </c>
-      <c r="E47" t="str">
-        <v>msk</v>
       </c>
     </row>
     <row r="48">
